--- a/Quiz_Ruolo_Conducenti_Revisionato.xlsx
+++ b/Quiz_Ruolo_Conducenti_Revisionato.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meroa\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meroa\Desktop\App Confluenze Milano\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA535D1-B6B0-4C66-A028-655FA982AB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF2C16A-9613-41EB-94A6-F5D631F62ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regolamento" sheetId="2" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="Geografia" sheetId="4" r:id="rId3"/>
     <sheet name="Inglese" sheetId="5" r:id="rId4"/>
     <sheet name="Francese" sheetId="6" r:id="rId5"/>
+    <sheet name="Tedesco" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5759" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5813" uniqueCount="2992">
   <si>
     <t>ID Domanda</t>
   </si>
@@ -8951,6 +8952,57 @@
   </si>
   <si>
     <t>Francese</t>
+  </si>
+  <si>
+    <t>Tedesco</t>
+  </si>
+  <si>
+    <t>Ich whone in Lecco und habe …... schones Haus</t>
+  </si>
+  <si>
+    <t>ein</t>
+  </si>
+  <si>
+    <t>eines</t>
+  </si>
+  <si>
+    <t>einem</t>
+  </si>
+  <si>
+    <t>…... Sie mir bitte sagen, wann das Konzert beginnt ?</t>
+  </si>
+  <si>
+    <t>Mochten</t>
+  </si>
+  <si>
+    <t>Konnten</t>
+  </si>
+  <si>
+    <t>Wollten</t>
+  </si>
+  <si>
+    <t>Ich habe heute bis 10.00 Uhr …...</t>
+  </si>
+  <si>
+    <t>schlafen</t>
+  </si>
+  <si>
+    <t>geschlafen</t>
+  </si>
+  <si>
+    <t>geschlaft</t>
+  </si>
+  <si>
+    <t>Ich gehe ….. Hause.</t>
+  </si>
+  <si>
+    <t>nach</t>
+  </si>
+  <si>
+    <t>von</t>
+  </si>
+  <si>
+    <t>aus</t>
   </si>
 </sst>
 </file>
@@ -31479,4 +31531,388 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AC7658-D8EF-4AEE-852F-09DDA5E8B681}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2969</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2978</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2982</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2983</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>2982</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2987</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2991</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>2989</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="7" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Quiz_Ruolo_Conducenti_Revisionato.xlsx
+++ b/Quiz_Ruolo_Conducenti_Revisionato.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meroa\Desktop\App Confluenze Milano\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF2C16A-9613-41EB-94A6-F5D631F62ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A76C357-A528-40F4-B7FC-E1D6121A9238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regolamento" sheetId="2" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="Inglese" sheetId="5" r:id="rId4"/>
     <sheet name="Francese" sheetId="6" r:id="rId5"/>
     <sheet name="Tedesco" sheetId="7" r:id="rId6"/>
+    <sheet name="Spagnolo" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5813" uniqueCount="2992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5867" uniqueCount="3009">
   <si>
     <t>ID Domanda</t>
   </si>
@@ -9003,6 +9004,57 @@
   </si>
   <si>
     <t>aus</t>
+  </si>
+  <si>
+    <t>Spagnolo</t>
+  </si>
+  <si>
+    <t>Juan trabaja en un bar, es …...</t>
+  </si>
+  <si>
+    <t>mecànico</t>
+  </si>
+  <si>
+    <t>restaurador</t>
+  </si>
+  <si>
+    <t>camarero</t>
+  </si>
+  <si>
+    <t>Estos zapatos son …. Caros.</t>
+  </si>
+  <si>
+    <t>muy</t>
+  </si>
+  <si>
+    <t>mucha</t>
+  </si>
+  <si>
+    <t>mucho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lola ….. casi siempre a las siete </t>
+  </si>
+  <si>
+    <t>despertar</t>
+  </si>
+  <si>
+    <t>se despierta</t>
+  </si>
+  <si>
+    <t>despierta</t>
+  </si>
+  <si>
+    <t>Elisa, ordena ….. cosas por favor.</t>
+  </si>
+  <si>
+    <t>tu</t>
+  </si>
+  <si>
+    <t>tuyas</t>
+  </si>
+  <si>
+    <t>tus</t>
   </si>
 </sst>
 </file>
@@ -31915,4 +31967,388 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9869AF7B-98EC-4318-8AB8-6C0141177632}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2969</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>2993</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2995</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2996</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>2998</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>3001</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3002</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>3007</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>3008</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="7" t="s">
+        <v>2992</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Quiz_Ruolo_Conducenti_Revisionato.xlsx
+++ b/Quiz_Ruolo_Conducenti_Revisionato.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meroa\Desktop\App Confluenze Milano\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meroa\Desktop\APP TAXI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A76C357-A528-40F4-B7FC-E1D6121A9238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81A1A84-347F-4142-BCEA-071982182514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regolamento" sheetId="2" r:id="rId1"/>
@@ -31571,7 +31571,7 @@
         <v>2968</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>2974</v>
